--- a/2026_DSAIML_Club_Batch/01 Advanced Excel/2026_03_05.xlsx
+++ b/2026_DSAIML_Club_Batch/01 Advanced Excel/2026_03_05.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\01 Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F511EC2D-343E-4395-83B1-4AC3D3950106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF92847-221F-4D63-9C37-39456401876B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{37280455-502C-4E64-A1C4-AB23CF952D93}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{37280455-502C-4E64-A1C4-AB23CF952D93}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Consolidated Marks Sheet" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <sheet name="Vraj Patel" sheetId="2" r:id="rId3"/>
+    <sheet name="Pushparaj Chavda" sheetId="3" r:id="rId4"/>
+    <sheet name="Krushnam Patel" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="61">
   <si>
     <t>Sr. No.</t>
   </si>
@@ -210,6 +211,9 @@
   </si>
   <si>
     <t>Pushparaj Chavda</t>
+  </si>
+  <si>
+    <t>Krushnam Patel</t>
   </si>
 </sst>
 </file>
@@ -1032,8 +1036,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C180A50B-2A11-4DE3-94D9-3F5D74137F14}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -1051,8 +1059,12 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <f>Sheet2!B1</f>
+        <f>'Vraj Patel'!B1</f>
         <v>Vraj Patel</v>
+      </c>
+      <c r="C2">
+        <f>'Vraj Patel'!E15</f>
+        <v>1141</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1060,8 +1072,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <f>Sheet3!B1</f>
+        <f>'Pushparaj Chavda'!B1</f>
         <v>Pushparaj Chavda</v>
+      </c>
+      <c r="C3">
+        <f>'Pushparaj Chavda'!E15</f>
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <f>'Krushnam Patel'!B1</f>
+        <v>Krushnam Patel</v>
+      </c>
+      <c r="C4">
+        <f>'Krushnam Patel'!E15</f>
+        <v>1229</v>
       </c>
     </row>
   </sheetData>
@@ -1788,4 +1817,366 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4653197B-B1B8-457F-A0B0-B81524667267}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>82</v>
+      </c>
+      <c r="D6">
+        <v>95</v>
+      </c>
+      <c r="E6">
+        <f>D6+C6</f>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7">
+        <v>94</v>
+      </c>
+      <c r="D7">
+        <v>97</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ref="E7:E8" si="0">D7+C7</f>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>86</v>
+      </c>
+      <c r="D8">
+        <v>90</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>82</v>
+      </c>
+      <c r="D9">
+        <v>90</v>
+      </c>
+      <c r="E9">
+        <f>D9+C9</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10">
+        <v>88</v>
+      </c>
+      <c r="D10">
+        <v>85</v>
+      </c>
+      <c r="E10">
+        <f>D10+C10</f>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>84</v>
+      </c>
+      <c r="D12">
+        <v>78</v>
+      </c>
+      <c r="E12">
+        <f t="shared" ref="E12:E13" si="1">D12+C12</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13">
+        <v>88</v>
+      </c>
+      <c r="D13">
+        <v>90</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15">
+        <f>SUM(C6:C13)</f>
+        <v>604</v>
+      </c>
+      <c r="D15">
+        <f>SUM(D6:D13)</f>
+        <v>625</v>
+      </c>
+      <c r="E15">
+        <f>SUM(E6:E13)</f>
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16">
+        <f>C15/7</f>
+        <v>86.285714285714292</v>
+      </c>
+      <c r="D16">
+        <f>D15/7</f>
+        <v>89.285714285714292</v>
+      </c>
+      <c r="E16">
+        <f>E15/7</f>
+        <v>175.57142857142858</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17">
+        <f>AVERAGE(C6:C13)</f>
+        <v>86.285714285714292</v>
+      </c>
+      <c r="D17">
+        <f>AVERAGE(D6:D13)</f>
+        <v>89.285714285714292</v>
+      </c>
+      <c r="E17">
+        <f>AVERAGE(E6:E13)</f>
+        <v>175.57142857142858</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18">
+        <f>ROUND(C17, 4)</f>
+        <v>86.285700000000006</v>
+      </c>
+      <c r="D18">
+        <f t="shared" ref="D18:E18" si="2">ROUND(D17, 4)</f>
+        <v>89.285700000000006</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>175.57140000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19">
+        <f>TRUNC(C17, 4)</f>
+        <v>86.285700000000006</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:E19" si="3">TRUNC(D17, 4)</f>
+        <v>89.285700000000006</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="3"/>
+        <v>175.57140000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20">
+        <f>ROUNDDOWN(C19, 2)</f>
+        <v>86.28</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ref="D20:E20" si="4">ROUNDDOWN(D19, 2)</f>
+        <v>89.28</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="4"/>
+        <v>175.57</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21">
+        <f>ROUNDUP(C17, 2)</f>
+        <v>86.29</v>
+      </c>
+      <c r="D21">
+        <f>ROUNDUP(D17, 2)</f>
+        <v>89.29</v>
+      </c>
+      <c r="E21">
+        <f>ROUNDUP(E16, 2)</f>
+        <v>175.57999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22">
+        <f>ROUND(C17, 0)</f>
+        <v>86</v>
+      </c>
+      <c r="D22">
+        <f t="shared" ref="D22:E22" si="5">ROUND(D17, 0)</f>
+        <v>89</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="5"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23">
+        <f>ROUND(C17, -1)</f>
+        <v>90</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ref="D23:E23" si="6">ROUND(D17, -1)</f>
+        <v>90</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="6"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24">
+        <f>ROUND(C17, -2)</f>
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <f t="shared" ref="D24:E24" si="7">ROUND(D17, -2)</f>
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>